--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,6 +720,242 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep01/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-24 20:33</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3d39f2a7045594e959767bec72c9b067_1784925178.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-24 20:37</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3cbb98cc7d620a272997d8d94b53f61d_1784925330.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-24 20:42</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f4381dd8e631efab3a61a33bbdf4e8c8_1784925586.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-24 20:44</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4f60c9004c5214ff7cc832c73a447eb3_1784925855.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep02/shots/shot_04.mp4</t>
         </is>
       </c>
     </row>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,6 +956,242 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7ac56b4f04f40d9fcf497f7734eb4395_1785190270.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6ea27e4d8b9045e8c516b754228ace36_1785190397.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/705ef353278e56c481d3ee6703bef6a8_1785190849.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f9ca376ab9a9cced316f6d99fa34f22b_1785190992.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep03/shots/shot_04.mp4</t>
         </is>
       </c>
     </row>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1195,242 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/83bb88e0722a472485a363d0d63a53cf_1785528378.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8fb3e220ab2d170bc930a6bd8888e9cd_1785528520.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d3f0099aa67e0eb343f809b2265e5c1f_1785528892.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b7e872299a33bbf923d6569bccb7a067_1785529019.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1431,6 +1431,242 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:47</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/16657236d7a7fd38309bf9b1c9d1bf60_1785613609.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:49</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8c2ca87b1b40938d26d6ffc06752f55a_1785613743.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:53</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ec5af8f9032d7a9391c34781e36c3a76_1785613876.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-01 19:57</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/90e387eed1988a8b03d0f477a7b9dc22_1785614114.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1667,6 +1667,242 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-02 19:49</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/99c8cf25da3ae5c6c055beca78edcd3d_1785700032.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-02 19:51</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ca9b2e78aac34cca0d3b00528b931a51_1785700273.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-02 19:57</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ab08f354f319a07518e3836d2620a37a_1785700409.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-02 19:59</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/473ec8bd951b2295e6498e0c77d6bc56_1785700766.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1903,6 +1903,242 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:16</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/76479ee202cf1b2598ade60047c4354c_1785788173.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:24</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b7177f71445940427b03d9d40002c563_1785788351.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1e84ec74fce84530d28be118b6c3c116_1785788796.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:30</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b21212ab0cd5089a28f35d41ebeb2099_1785788973.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,6 +2139,478 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-07 18:09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/902d67be9f9159f9e53100594466eef8_1786125848.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-07 18:11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3243c197ee0549abcc8bea049ab62071_1786126240.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-07 18:13</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b7b985845c44632452001f04a6a48669_1786126355.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-07 18:15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a432976235bd0edcbf1445a53c73d7e9_1786126486.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-07 19:15</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ec9dbe480cde0d64688095a3d1c0da9b_1786130110.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-07 19:20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/80a21dddfefe6aabb46436ac0e319a30_1786130250.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-07 19:26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/37a69330b6edd59b7c39efdc9d4b5b7e_1786130522.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-07 19:31</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bc31fd72e9b17148b84920a3129cc07b_1786130909.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2611,6 +2611,242 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-08 19:11</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7d2cc06e6c5ef80007cef78da06d1245_1786216258.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-08 19:14</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7326d5f5acf2a728708bdcdaa0655ca1_1786216409.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-08 19:16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d40d7143cd9317f5d3cef4eea381b6b2_1786216565.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-08 19:20</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5c1f604b82cde14018309fbaf5066e03_1786216686.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2847,6 +2847,242 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-09 19:15</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cb3bef1e303caae8f0d102bb703fa504_1786302880.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-09 19:19</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6e75a200f285719ef3a3b81af7a8bb94_1786303026.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-09 19:23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/702043a64a022ae5bd44eb3df7018a57_1786303266.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-09 19:25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a90f0dfac5633645e9ce590879307e12_1786303498.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep10/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3083,6 +3083,242 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-13 19:40</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c4963949a6e3ae729b6e82d9316280cc_1786650009.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-13 19:43</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a4fba97cc6de0e224d139687f1afd78e_1786650165.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep11/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-13 19:46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e41c7757f0a6dc5c42944d6147e53aed_1786650313.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep11/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-13 19:49</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4c02efb51bcca23669cc549109dee828_1786650496.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep11/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3319,6 +3319,242 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:33</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b676cc02ad25eb8456b9bd7c589e699a_1786735948.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:36</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ae997e60165d65a365e9b5af1705bea9_1786736136.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep12/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:39</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/41e7d388299c43c40b60428b4b0d67fa_1786736306.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep12/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:41</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5e0ee786b85214a5a386901e0a488bb9_1786736461.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep12/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3555,6 +3555,242 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-15 19:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/53de2e5e1012045f67ee60167a2163f2_1786820365.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep13/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-15 19:03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/848218e081dc9758badb47545d205633_1786820557.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep13/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-15 19:06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6a339027fb8e992a5bae3679211551a5_1786820729.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep13/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-15 19:08</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e3a7d94269660c58db9b948f846644ca_1786820885.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep13/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3791,6 +3791,242 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-16 18:59</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6ab54bb3beaa855122a9e989a954f84f_1786906747.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep14/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-16 19:04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8fb082a9c06936d4a022ce79ef8f7987_1786906931.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep14/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-16 19:06</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2fad99d7af3566ee7da690cc0c9d83de_1786907140.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep14/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-16 19:08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/800a015be562c93fb4c77d3f978866e3_1786907260.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep14/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4027,6 +4027,242 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-17 19:13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/08e6f3c8c3282447577b5032beefc9c8_1786993890.mp4</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep15/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-17 19:17</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b3b486e9c144056e45cc8a9677588386_1786994081.mp4</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep15/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-17 19:20</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/13f75575aedf174e900dc426d474ea44_1786994390.mp4</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep15/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-17 19:24</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ea74ae36533fc6cab81f0a7fe54a703a_1786994550.mp4</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep15/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4263,6 +4263,242 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-18 19:15</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ec7476a20cda0cd9f2db3489b43b127c_1787080365.mp4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep16/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-18 19:19</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4ffdbd2e8a6e8b5df334bf34d33b6a36_1787080657.mp4</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep16/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-18 19:21</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e496f2403a398c155aa3a21808ea0cdf_1787080846.mp4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep16/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-18 19:23</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/05865669d98df63283977346d1f0180a_1787080986.mp4</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep16/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4499,6 +4499,242 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-19 19:15</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ef82edf68f03db025d84b3d6c97d415a_1787166627.mp4</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep17/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-19 19:22</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2549e0805cdc673dc51fde19c39ee187_1787167035.mp4</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep17/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-19 19:32</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c128c0b83e5f06b29e11b60d37b897f1_1787167436.mp4</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep17/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-19 19:39</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ffb2b6f5724f9a140913fd369d59c0b7_1787168116.mp4</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep17/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4735,6 +4735,242 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:14</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3cd64582fb3e445850680a19576739f4_1787253212.mp4</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep18/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:16</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ef7414e682e95bfc727d6905ebfad55d_1787253338.mp4</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep18/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:18</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a2c8f89d6b0e53eb438b9d996242be2f_1787253481.mp4</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep18/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-20 19:20</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ad95fd59fe7a90a90cdad876a741d8f0_1787253612.mp4</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep18/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4971,6 +4971,242 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-21 19:13</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b370bee5aa233e888c2377553ecad9ab_1787339357.mp4</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep19/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-21 19:17</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e22c6833d3e379b24817e5e49d9c9d5a_1787339810.mp4</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep19/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-21 19:20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5ddb02866f12439b0c31d9c2e72de0e3_1787339969.mp4</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep19/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-21 19:21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/977d7a19eb27f8ca15be01664a0a0172_1787340097.mp4</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep19/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5207,6 +5207,242 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-22 19:03</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1473843afa56626e438028f079bf2104_1787425389.mp4</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep20/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-22 19:06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a62de2d349690bb3f5a10dfc5815a2af_1787425528.mp4</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep20/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-22 19:10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6aaa8f16b9c87d510576fbb7780dc714_1787425664.mp4</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep20/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-22 19:13</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d4c7a3f59a153fb3695ce60ab8f63ada_1787425903.mp4</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep20/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5443,6 +5443,242 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-23 19:01</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cf6524f5062b8280ed36ee066a317f6b_1787511596.mp4</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep21/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-23 19:03</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f9888c2f8807605afd7ee11d2b0920ad_1787511792.mp4</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep21/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-23 19:06</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/aefc5009b5d94bd40d9c7d59f3a2239d_1787511935.mp4</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep21/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-23 19:08</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/574d7937d6a2fbfe964f589b1f06da44_1787512108.mp4</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep21/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5679,6 +5679,387 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-24 19:16</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/412df3b5fd6513abeadd88f2f36727a7_1787598750.mp4</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep22/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:43</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>environment_ref_kitchen_counter</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/v4K14Bss/kitchen-counter.png</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/environments/kitchen_counter.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:44</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/M51yVx71/ep22-lemon.png</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep22_lemon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:47</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6e8fb1a89e1c35f3f016a7231e6f7c69_1787949962.mp4</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep22/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:50</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/aea8f7f39e900ad03eb6707d462001df_1787950142.mp4</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep22/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:52</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6845643760dfaaaf92c7ebb3a818057e_1787950330.mp4</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep22/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-28 21:02</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/74946f85ea0aeb7d9642c2b1e99d86eb_1787950519.mp4</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep22/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6060,6 +6060,1023 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:06</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>environment_ref_bathroom_sink</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/M5jcPDhL/bathroom-sink.png</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/environments/bathroom_sink.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/SXPpVG4t/ep23-bar-of-soap.png</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep23_bar_of_soap.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4cc5cb269892b71fec9e62d245470493_1788037787.mp4</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep23/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:12</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/35bb3e362d651eff54f215df23937ea0_1788037929.mp4</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep23/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-01 16:43</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/rGBZn5JK/ep24-coffee-mug.png</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep24_coffee_mug.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:05</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8b373af13c358260c7ba1c0e487af7e7_1788282072.mp4</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep24/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-01 19:11</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>environment_ref_living_room_table</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/ZRvqsg7d/living-room-table.png</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/environments/living_room_table.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-01 19:13</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/nMWY5Z5h/ep25-tennis-ball.png</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep25_tennis_ball.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-01 19:17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/202e4f6bd9d772f8dccb4570893c14a1_1788290193.mp4</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep25/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-02 03:36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/nqvdRLHT/ep26-metal-fork.png</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep26_metal_fork.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-02 05:08</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9c50a366f170ceb8f67f303ab4ca3c85_1788325701.mp4</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep26/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-02 05:35</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/af94c5f3fce0f46f8a975865884cc30f_1788327294.mp4</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep26/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-02 05:38</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/945684b5d51309bbb8f06b5e51ebd348_1788327483.mp4</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep26/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-02 05:42</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5a21921e335687a41170e9b1d68c4c0f_1788327726.mp4</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep26/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:15</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/SwYP4f5F/ep27-ice-cube.png</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep27_ice_cube.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:20</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c2c0ec0f916972f7852e0f9b044a31ff_1788369436.mp4</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep27/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3a85a686e1c5e908fcb4802a3f64f4b0_1788369753.mp4</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep27/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:35</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/227be241b0234c50642948cb8388450a_1788370169.mp4</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep27/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:44</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1cc0779a90eafea732764fca53548678_1788370690.mp4</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep27/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7077,6 +7077,548 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:17</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/HfR2WyZ8/ep28-honey-jar.png</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep28_honey_jar.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:20</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1103427e5a9577d0d4514dd96eeb7a46_1788470397.mp4</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep28/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:30</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a43851d3cea4018f441cdb97b33b8ebf_1788470630.mp4</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep28/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:37</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ccac32a6673c3977913af7b4c8b3bc10_1788471162.mp4</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep28/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/50460f43a9d05fe2cad69d30f1ecd6ab_1788471532.mp4</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep28/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:59</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/5hbsbjkV/ep29-bar-of-soap.png</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep29_bar_of_soap.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:09</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f20b7bd9d879fa823c50661ef7e5449f_1788555731.mp4</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep29/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5e09a59118697f931cfc99b7f7a2e93c_1788556292.mp4</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep29/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9f6df501a6ef7a0e9bf438594740bf20_1788556527.mp4</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep29/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:27</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ab7c854820b2bcfb3196dad112067ba7_1788556895.mp4</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep29/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7619,6 +7619,658 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-05 20:41</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/jZR7hLtB/ep30-yellow-banana.png</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep30_yellow_banana.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-05 20:47</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6111c3abfeadc297a2fbcebd839782a3_1788640988.mp4</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep30/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-05 20:49</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/710449cc8507ee93b5bb39471e41f002_1788641347.mp4</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep30/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-05 20:56</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e6a1ea0f09e435cb525a7a3d38ca659f_1788641502.mp4</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep30/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:52</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8bf0c2f0637267ab37f625b4f9d7d570_1788817932.mp4</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep30/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:55</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/936318dd36f9671be73c88193284f120_1788818073.mp4</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep30/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:57</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/398f07a43d85ff6f5afb0ae9fce25e0c_1788818239.mp4</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep30/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/Dn8SmY2/ep31-plastic-water-bottle.png</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep31_plastic_water_bottle.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:08</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6ea83513289e9828087dd42984398b57_1788818726.mp4</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep31/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a8b3e36a684546b22041694fd46d65d8_1788819011.mp4</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep31/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:13</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1ae962dff7f459a3051fcba43cdb220b_1788819157.mp4</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep31/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:15</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0681480b61fc66d8591b55aa3a6fa0b0_1788819295.mp4</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep31/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8271,6 +8271,277 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:33</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/C5DhBhxg/ep32-folded-white-cloth-napkin.png</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep32_folded_white_cloth_napkin.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:37</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b6d9ec43b8d36884765723e73ef69b48_1788903448.mp4</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep32/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:42</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/86803fe7814ee650564bf3730021ae40_1788903580.mp4</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep32/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:48</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9bc90ba2e03d3fd1d97910dacdb4a68f_1788903831.mp4</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep32/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:51</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5c867641a35e7ce9d4da9814c5ecaf51_1788904232.mp4</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep32/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/unnatural-lab/series_log.xlsx
+++ b/sentinal_ihsan/unnatural-lab/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8542,6 +8542,497 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-09 21:09</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>object_ref</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>https://i.ibb.co/zh8KJ6mD/ep33-lemon.png</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/refs/props/ep33_lemon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-09 21:18</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c6d9db7b50458b487143a4393bf17601_1788988367.mp4</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep33/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-09 21:21</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/72990d79dda84f127e33afe3a354dec0_1788988822.mp4</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep33/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-09 21:27</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/427edc3aaf04f89e166635fe4683217d_1788989002.mp4</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep33/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-09 21:30</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/64f2f3b9c2f647acbfab2a0f0ed527be_1788989372.mp4</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep33/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-10 21:11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cf34bccff22570808dc838ba12ce81d7_1789074634.mp4</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep33/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-10 21:12</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/67aea4a8b37aba92cb13034f953c78c3_1789074747.mp4</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep33/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-10 21:15</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/36244de21af4c013bf70fc345ff060bb_1789074878.mp4</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep33/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-10 21:17</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3f502dfa57d09768f6e2555192a254b8_1789075041.mp4</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/unnatural-lab/episodes/ep33/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
